--- a/Tests/Homepage/Homepage_Fail.xlsx
+++ b/Tests/Homepage/Homepage_Fail.xlsx
@@ -130,7 +130,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -155,7 +155,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -180,7 +180,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -205,7 +205,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -230,7 +230,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -255,7 +255,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -280,7 +280,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -305,7 +305,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -330,7 +330,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -355,7 +355,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -380,7 +380,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -405,7 +405,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -430,7 +430,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -455,7 +455,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -480,7 +480,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -505,7 +505,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -530,7 +530,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -555,7 +555,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -899,7 +899,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>https://dev.marcjacobs.com/us-en/homepage</t>
@@ -907,12 +907,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_2561</t>
+          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HSH009H01/NRF/617/Sequence/MAIN/?preset=PLP_615</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No results for url found: consider case sensitivity</t>
+          <t>WebDriver error: Message: timeout: Timed out receiving message from</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_1920</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_2561</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_1440</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_1920</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_768</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_1440</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_MOBILE/?preset=4COL_0</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_768</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_2561</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_MOBILE/?preset=4COL_0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_1920</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_2561</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_1440</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_1920</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_768</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_1440</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_MOBILE/?preset=4COL_0</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_768</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_2561</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_MOBILE/?preset=4COL_0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_1920</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_2561</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_1440</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_1920</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_768</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_1440</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_MOBILE/?preset=4COL_0</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_768</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_MOBILE_JP_V3/?preset=4COL_0</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_MOBILE/?preset=4COL_0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://cdn.media.amplience.net/i/Marc_Jacobs/SP26_SEARCH_DESKTOP?fmt=auto&amp;w=1600&amp;qlt=50</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_MOBILE_JP_V3/?preset=4COL_0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Amplience found in URL</t>
+          <t>No results for url found: consider case sensitivity</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1196,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>https://cdn.media.amplience.net/i/Marc_Jacobs/SP26_SEARCH_DESKTOP?fmt=auto&amp;w=1600&amp;qlt=50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Amplience found in URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://dev.marcjacobs.com/us-en/homepage</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>https://cdn.media.amplience.net/i/Marc_Jacobs/SP26_SEARCH_MOBILE?fmt=auto&amp;w=800&amp;qlt=50</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Amplience found in URL</t>
         </is>

--- a/Tests/Homepage/Homepage_Fail.xlsx
+++ b/Tests/Homepage/Homepage_Fail.xlsx
@@ -130,17 +130,42 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -161,11 +186,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -186,11 +211,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -211,11 +236,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -236,11 +261,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -261,11 +286,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -286,11 +311,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -311,11 +336,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -336,11 +361,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -361,11 +386,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -386,11 +411,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -411,11 +436,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -436,11 +461,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -461,11 +486,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -486,86 +511,11 @@
     <ext cx="1905000" cy="1905000"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1905000"/>
-    <pic>
-      <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1905000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="1905000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -868,7 +818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -899,7 +849,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="150" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>https://dev.marcjacobs.com/us-en/homepage</t>
@@ -907,12 +857,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/Product_Style_Code/2S6HSH009H01/NRF/617/Sequence/MAIN/?preset=PLP_615</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_MOBILE_JP_V3/?preset=4COL_0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WebDriver error: Message: timeout: Timed out receiving message from</t>
+          <t>No results for url found: consider case sensitivity</t>
         </is>
       </c>
     </row>
@@ -924,7 +874,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_2561</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_1_DESKTOP/?preset=3COL_2561</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -941,7 +891,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_1920</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_1_DESKTOP/?preset=3COL_1920</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -958,7 +908,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_1440</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_1_DESKTOP/?preset=3COL_1440</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -975,7 +925,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_DESKTOP/?preset=4COL_768</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_1_DESKTOP/?preset=3COL_768</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -992,7 +942,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_WALLETS_MOBILE/?preset=4COL_0</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_1_MOBILE/?preset=3COL_0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1009,7 +959,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_2561</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_2_DESKTOP/?preset=3COL_2561</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1026,7 +976,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_1920</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_2_DESKTOP/?preset=3COL_1920</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1043,7 +993,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_1440</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_2_DESKTOP/?preset=3COL_1440</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1060,7 +1010,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_DESKTOP/?preset=4COL_768</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_2_DESKTOP/?preset=3COL_768</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1077,7 +1027,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SNAPSHOT_MOBILE/?preset=4COL_0</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_2_MOBILE/?preset=3COL_0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1094,7 +1044,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_2561</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_3_DESKTOP/?preset=3COL_2561</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1111,7 +1061,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_1920</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_3_DESKTOP/?preset=3COL_1920</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1128,7 +1078,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_1440</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_3_DESKTOP/?preset=3COL_1440</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1145,7 +1095,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_DESKTOP/?preset=4COL_768</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_3_DESKTOP/?preset=3COL_768</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1162,63 +1112,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_TOTES_MOBILE/?preset=4COL_0</t>
+          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260305_HP_EXPLORE_3_MOBILE/?preset=3COL_0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>No results for url found: consider case sensitivity</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>https://dev.marcjacobs.com/us-en/homepage</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://marcjacobs.bynder.com/match/MJ_Filename/260205_NAV_SHOES_MOBILE_JP_V3/?preset=4COL_0</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>No results for url found: consider case sensitivity</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>https://dev.marcjacobs.com/us-en/homepage</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://cdn.media.amplience.net/i/Marc_Jacobs/SP26_SEARCH_DESKTOP?fmt=auto&amp;w=1600&amp;qlt=50</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Amplience found in URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>https://dev.marcjacobs.com/us-en/homepage</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://cdn.media.amplience.net/i/Marc_Jacobs/SP26_SEARCH_MOBILE?fmt=auto&amp;w=800&amp;qlt=50</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Amplience found in URL</t>
         </is>
       </c>
     </row>
